--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98302</v>
+        <v>98303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40692-2026 artfynd.xlsx
+++ b/artfynd/A 40692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137008088</v>
       </c>
       <c r="B2" t="n">
-        <v>98303</v>
+        <v>98306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
